--- a/docs/downloads/13/tbl_synthese_qualite_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_alaotra_ambohidrony.xlsx
@@ -452,9 +452,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
